--- a/partial/sliding_window_results_window_10.xlsx
+++ b/partial/sliding_window_results_window_10.xlsx
@@ -463,13 +463,13 @@
         <v>29.92</v>
       </c>
       <c r="C2" t="n">
-        <v>30.15045815484523</v>
+        <v>30.02419053477981</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2304581548452305</v>
+        <v>0.1041905347798036</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05311096113466823</v>
+        <v>0.01085566753770145</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.98</v>
       </c>
       <c r="C3" t="n">
-        <v>29.57760358353954</v>
+        <v>30.02977761739633</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.4023964164604585</v>
+        <v>0.04977761739632669</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1619228759802188</v>
+        <v>0.002477811193655085</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>30.04</v>
       </c>
       <c r="C4" t="n">
-        <v>29.8876133789907</v>
+        <v>30.07035366584773</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.152386621009299</v>
+        <v>0.03035366584772703</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02322168226263173</v>
+        <v>0.0009213450303954703</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>30.21</v>
       </c>
       <c r="C5" t="n">
-        <v>29.55110988573279</v>
+        <v>30.08315331313932</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6588901142672086</v>
+        <v>-0.1268466868606843</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4341361826790551</v>
+        <v>0.01609008196753251</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>30.22</v>
       </c>
       <c r="C6" t="n">
-        <v>29.94462543628945</v>
+        <v>30.19825301488454</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2753745637105496</v>
+        <v>-0.02174698511546325</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07583115033877554</v>
+        <v>0.00047293136161218</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>30.38</v>
       </c>
       <c r="C7" t="n">
-        <v>29.8816698068154</v>
+        <v>30.25568284039331</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4983301931846036</v>
+        <v>-0.1243171596066937</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2483329814394043</v>
+        <v>0.01545475617267614</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>30.44</v>
       </c>
       <c r="C8" t="n">
-        <v>30.53153397042876</v>
+        <v>30.54227831882804</v>
       </c>
       <c r="D8" t="n">
-        <v>0.09153397042875966</v>
+        <v>0.1022783188280414</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008378467742453048</v>
+        <v>0.01046085450229049</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>30.48</v>
       </c>
       <c r="C9" t="n">
-        <v>30.37329085993156</v>
+        <v>30.5519949621441</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1067091400684426</v>
+        <v>0.07199496214410317</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01138684057414649</v>
+        <v>0.005183274574130849</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.69</v>
       </c>
       <c r="C10" t="n">
-        <v>30.56229443542715</v>
+        <v>30.60082321928214</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1277055645728531</v>
+        <v>-0.08917678071786383</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01630871122287115</v>
+        <v>0.007952498219201971</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.75</v>
       </c>
       <c r="C11" t="n">
-        <v>30.40295983610252</v>
+        <v>30.76713189625077</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.347040163897482</v>
+        <v>0.01713189625076694</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1204368753579912</v>
+        <v>0.0002935018691470424</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.94</v>
       </c>
       <c r="C12" t="n">
-        <v>30.6690536612905</v>
+        <v>30.89341029886786</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2709463387094964</v>
+        <v>-0.04658970113214522</v>
       </c>
       <c r="E12" t="n">
-        <v>0.07341191846008112</v>
+        <v>0.002170600251582614</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.95</v>
       </c>
       <c r="C13" t="n">
-        <v>30.87308474573936</v>
+        <v>31.10379906852334</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.07691525426064416</v>
+        <v>0.1537990685233375</v>
       </c>
       <c r="E13" t="n">
-        <v>0.00591595633797954</v>
+        <v>0.02365415347864626</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>31.02</v>
       </c>
       <c r="C14" t="n">
-        <v>31.42862978224556</v>
+        <v>31.27142860609367</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4086297822455585</v>
+        <v>0.2514286060936683</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1669782989380525</v>
+        <v>0.06321634396220505</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>31.12</v>
       </c>
       <c r="C15" t="n">
-        <v>31.73932379059798</v>
+        <v>31.33366433097254</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6193237905979778</v>
+        <v>0.2136643309725379</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3835619576006479</v>
+        <v>0.04565244632994222</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>31.28</v>
       </c>
       <c r="C16" t="n">
-        <v>31.8001027920917</v>
+        <v>31.1674750055018</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5201027920916985</v>
+        <v>-0.1125249944982052</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2705069143415806</v>
+        <v>0.01266187438682111</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>31.38</v>
       </c>
       <c r="C17" t="n">
-        <v>31.4866341557887</v>
+        <v>30.93389696060447</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1066341557887007</v>
+        <v>-0.4461030393955276</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0113708431807689</v>
+        <v>0.1990079217579277</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>31.58</v>
       </c>
       <c r="C18" t="n">
-        <v>31.84267344671913</v>
+        <v>31.12874365607843</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2626734467191341</v>
+        <v>-0.4512563439215675</v>
       </c>
       <c r="E18" t="n">
-        <v>0.06899733961130976</v>
+        <v>0.2036322879294601</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>31.65</v>
       </c>
       <c r="C19" t="n">
-        <v>31.82384162411077</v>
+        <v>31.68285551433151</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1738416241107714</v>
+        <v>0.03285551433151213</v>
       </c>
       <c r="E19" t="n">
-        <v>0.03022091027347074</v>
+        <v>0.001079484821988199</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.88</v>
       </c>
       <c r="C20" t="n">
-        <v>32.52588862827167</v>
+        <v>32.54857965831769</v>
       </c>
       <c r="D20" t="n">
-        <v>0.645888628271674</v>
+        <v>0.6685796583176931</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4171721201306647</v>
+        <v>0.4469987595162032</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>32.28</v>
       </c>
       <c r="C21" t="n">
-        <v>32.42675507501861</v>
+        <v>32.55971918219023</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1467550750186106</v>
+        <v>0.2797191821902274</v>
       </c>
       <c r="E21" t="n">
-        <v>0.02153705204371803</v>
+        <v>0.07824282088516962</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>32.45</v>
       </c>
       <c r="C22" t="n">
-        <v>32.48906773209526</v>
+        <v>32.73532906098168</v>
       </c>
       <c r="D22" t="n">
-        <v>0.03906773209525483</v>
+        <v>0.2853290609816739</v>
       </c>
       <c r="E22" t="n">
-        <v>0.001526287691066604</v>
+        <v>0.08141267304068377</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>32.85</v>
       </c>
       <c r="C23" t="n">
-        <v>32.68757766467187</v>
+        <v>32.9375852778052</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1624223353281309</v>
+        <v>0.08758527780519643</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0263810150134438</v>
+        <v>0.007671180888213434</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>32.9</v>
       </c>
       <c r="C24" t="n">
-        <v>32.81789647584993</v>
+        <v>32.99351977061944</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.08210352415007094</v>
+        <v>0.09351977061943728</v>
       </c>
       <c r="E24" t="n">
-        <v>0.006740988677861282</v>
+        <v>0.008745947496712165</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>33.1</v>
       </c>
       <c r="C25" t="n">
-        <v>33.14090606419386</v>
+        <v>33.22201537420774</v>
       </c>
       <c r="D25" t="n">
-        <v>0.04090606419386233</v>
+        <v>0.1220153742077414</v>
       </c>
       <c r="E25" t="n">
-        <v>0.001673306087832386</v>
+        <v>0.01488775154305518</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>33.4</v>
       </c>
       <c r="C26" t="n">
-        <v>33.68519413220316</v>
+        <v>33.51113863081579</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2851941322031664</v>
+        <v>0.1111386308157876</v>
       </c>
       <c r="E26" t="n">
-        <v>0.08133569304311714</v>
+        <v>0.01235179525960793</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>33.7</v>
       </c>
       <c r="C27" t="n">
-        <v>33.87216588000717</v>
+        <v>33.60283648162176</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1721658800071708</v>
+        <v>-0.09716351837824533</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02964109023864354</v>
+        <v>0.009440749303639617</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>34.1</v>
       </c>
       <c r="C28" t="n">
-        <v>33.97085561693148</v>
+        <v>33.71172498514026</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1291443830685211</v>
+        <v>-0.3882750148597438</v>
       </c>
       <c r="E28" t="n">
-        <v>0.01667827167814891</v>
+        <v>0.1507574871643343</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>34.4</v>
       </c>
       <c r="C29" t="n">
-        <v>34.27075136985163</v>
+        <v>34.29938866808003</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1292486301483677</v>
+        <v>-0.1006113319199713</v>
       </c>
       <c r="E29" t="n">
-        <v>0.01670520839522955</v>
+        <v>0.01012264011071063</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>34.9</v>
       </c>
       <c r="C30" t="n">
-        <v>34.61143521302103</v>
+        <v>34.59425327533567</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.2885647869789665</v>
+        <v>-0.3057467246643242</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0832696362842163</v>
+        <v>0.09348105964296206</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>35.3</v>
       </c>
       <c r="C31" t="n">
-        <v>35.35959892399529</v>
+        <v>35.63727115299272</v>
       </c>
       <c r="D31" t="n">
-        <v>0.05959892399529565</v>
+        <v>0.3372711529927201</v>
       </c>
       <c r="E31" t="n">
-        <v>0.003552031741397028</v>
+        <v>0.1137518306410388</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>35.7</v>
       </c>
       <c r="C32" t="n">
-        <v>35.79080162479443</v>
+        <v>35.89773605532633</v>
       </c>
       <c r="D32" t="n">
-        <v>0.09080162479442322</v>
+        <v>0.1977360553263239</v>
       </c>
       <c r="E32" t="n">
-        <v>0.008244935065307213</v>
+        <v>0.03909954757601502</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>36.3</v>
       </c>
       <c r="C33" t="n">
-        <v>36.03264968725425</v>
+        <v>36.32664756839336</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.2673503127457479</v>
+        <v>0.02664756839336491</v>
       </c>
       <c r="E33" t="n">
-        <v>0.07147618972524923</v>
+        <v>0.0007100929012790603</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>36.8</v>
       </c>
       <c r="C34" t="n">
-        <v>36.98082208978937</v>
+        <v>36.82917752352359</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1808220897893733</v>
+        <v>0.02917752352359315</v>
       </c>
       <c r="E34" t="n">
-        <v>0.03269662815579618</v>
+        <v>0.0008513278789698317</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>37.3</v>
       </c>
       <c r="C35" t="n">
-        <v>37.03808174720831</v>
+        <v>36.99573242149806</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2619182527916877</v>
+        <v>-0.3042675785019355</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0686011711454504</v>
+        <v>0.0925787593274315</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>37.9</v>
       </c>
       <c r="C36" t="n">
-        <v>38.01083806580366</v>
+        <v>37.78072258726555</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1108380658036623</v>
+        <v>-0.1192774127344478</v>
       </c>
       <c r="E36" t="n">
-        <v>0.01228507683109697</v>
+        <v>0.01422710118862381</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>38.5</v>
       </c>
       <c r="C37" t="n">
-        <v>38.67005654805641</v>
+        <v>38.52270208870895</v>
       </c>
       <c r="D37" t="n">
-        <v>0.170056548056408</v>
+        <v>0.02270208870894663</v>
       </c>
       <c r="E37" t="n">
-        <v>0.02891922953686141</v>
+        <v>0.0005153848317488821</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>38.9</v>
       </c>
       <c r="C38" t="n">
-        <v>39.12237970160986</v>
+        <v>39.12314879822863</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2223797016098601</v>
+        <v>0.2231487982286282</v>
       </c>
       <c r="E38" t="n">
-        <v>0.04945273168809041</v>
+        <v>0.04979538615088103</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>39.4</v>
       </c>
       <c r="C39" t="n">
-        <v>39.56793608028836</v>
+        <v>39.44146703013038</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1679360802883636</v>
+        <v>0.04146703013037722</v>
       </c>
       <c r="E39" t="n">
-        <v>0.02820252706261971</v>
+        <v>0.001719514587833613</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>39.9</v>
       </c>
       <c r="C40" t="n">
-        <v>39.85061662806815</v>
+        <v>39.72263802358091</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.04938337193184594</v>
+        <v>-0.1773619764190926</v>
       </c>
       <c r="E40" t="n">
-        <v>0.00243871742335903</v>
+        <v>0.03145727067928675</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>40.1</v>
       </c>
       <c r="C41" t="n">
-        <v>39.99719629544344</v>
+        <v>39.7702638787822</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1028037045565569</v>
+        <v>-0.3297361212177989</v>
       </c>
       <c r="E41" t="n">
-        <v>0.01056860167055183</v>
+        <v>0.108725909635759</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>40.6</v>
       </c>
       <c r="C42" t="n">
-        <v>40.14740321345568</v>
+        <v>39.90697336106128</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4525967865443263</v>
+        <v>-0.6930266389387256</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2048438511902505</v>
+        <v>0.4802859222787068</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>40.9</v>
       </c>
       <c r="C43" t="n">
-        <v>40.43717594502318</v>
+        <v>40.19635090321012</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4628240549768208</v>
+        <v>-0.7036490967898743</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2142061058651872</v>
+        <v>0.4951220514132059</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>41.2</v>
       </c>
       <c r="C44" t="n">
-        <v>41.25164687007472</v>
+        <v>41.21758245333769</v>
       </c>
       <c r="D44" t="n">
-        <v>0.05164687007471258</v>
+        <v>0.01758245333768826</v>
       </c>
       <c r="E44" t="n">
-        <v>0.002667399188514242</v>
+        <v>0.0003091426653719852</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>41.5</v>
       </c>
       <c r="C45" t="n">
-        <v>41.50640795799717</v>
+        <v>41.28955640879663</v>
       </c>
       <c r="D45" t="n">
-        <v>0.006407957997168978</v>
+        <v>-0.2104435912033651</v>
       </c>
       <c r="E45" t="n">
-        <v>4.106192569348186e-05</v>
+        <v>0.04428650507856904</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>41.8</v>
       </c>
       <c r="C46" t="n">
-        <v>42.16556872913132</v>
+        <v>41.71509244587822</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3655687291313257</v>
+        <v>-0.0849075541217772</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1336404957186925</v>
+        <v>0.007209292746942523</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>42.2</v>
       </c>
       <c r="C47" t="n">
-        <v>42.57779146628009</v>
+        <v>42.40166043411897</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3777914662800868</v>
+        <v>0.2016604341189705</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1427263919940579</v>
+        <v>0.04066693068905164</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>42.7</v>
       </c>
       <c r="C48" t="n">
-        <v>43.73722680448905</v>
+        <v>43.53255751544864</v>
       </c>
       <c r="D48" t="n">
-        <v>1.037226804489052</v>
+        <v>0.8325575154486344</v>
       </c>
       <c r="E48" t="n">
-        <v>1.07583944395057</v>
+        <v>0.6931520165300031</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>43.7</v>
       </c>
       <c r="C49" t="n">
-        <v>44.37882933852995</v>
+        <v>43.95549435339204</v>
       </c>
       <c r="D49" t="n">
-        <v>0.6788293385299511</v>
+        <v>0.255494353392038</v>
       </c>
       <c r="E49" t="n">
-        <v>0.4608092708490109</v>
+        <v>0.06527736461521558</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>44.2</v>
       </c>
       <c r="C50" t="n">
-        <v>43.9873501350492</v>
+        <v>44.25777747149995</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.212649864950798</v>
+        <v>0.05777747149994639</v>
       </c>
       <c r="E50" t="n">
-        <v>0.04521996506359261</v>
+        <v>0.003338236212927117</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>45.6</v>
       </c>
       <c r="C51" t="n">
-        <v>44.27202124572106</v>
+        <v>45.62681281157661</v>
       </c>
       <c r="D51" t="n">
-        <v>-1.327978754278938</v>
+        <v>0.02681281157660464</v>
       </c>
       <c r="E51" t="n">
-        <v>1.76352757181624</v>
+        <v>0.000718926864642504</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>0.4173962968654372</v>
+        <v>0.01236847578596567</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>7.226650934367638</v>
+        <v>3.819149214691712</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.1445330186873527</v>
+        <v>0.07638298429383424</v>
       </c>
     </row>
   </sheetData>

--- a/partial/sliding_window_results_window_10.xlsx
+++ b/partial/sliding_window_results_window_10.xlsx
@@ -463,13 +463,13 @@
         <v>29.92</v>
       </c>
       <c r="C2" t="n">
-        <v>30.02419053477981</v>
+        <v>29.86740087032578</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1041905347798036</v>
+        <v>-0.05259912967422053</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01085566753770145</v>
+        <v>0.002766668442485467</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.98</v>
       </c>
       <c r="C3" t="n">
-        <v>30.02977761739633</v>
+        <v>29.6750218361804</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04977761739632669</v>
+        <v>-0.3049781638195981</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002477811193655085</v>
+        <v>0.0930116804067736</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>30.04</v>
       </c>
       <c r="C4" t="n">
-        <v>30.07035366584773</v>
+        <v>29.91236588521106</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03035366584772703</v>
+        <v>-0.1276341147889362</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0009213450303954703</v>
+        <v>0.01629046725795533</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>30.21</v>
       </c>
       <c r="C5" t="n">
-        <v>30.08315331313932</v>
+        <v>29.89820336105438</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1268466868606843</v>
+        <v>-0.3117966389456228</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01609008196753251</v>
+        <v>0.09721714405778707</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>30.22</v>
       </c>
       <c r="C6" t="n">
-        <v>30.19825301488454</v>
+        <v>30.10612490490114</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.02174698511546325</v>
+        <v>-0.1138750950988552</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00047293136161218</v>
+        <v>0.01296753728377331</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>30.38</v>
       </c>
       <c r="C7" t="n">
-        <v>30.25568284039331</v>
+        <v>30.22249860450155</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1243171596066937</v>
+        <v>-0.1575013954984534</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01545475617267614</v>
+        <v>0.02480668958396025</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>30.44</v>
       </c>
       <c r="C8" t="n">
-        <v>30.54227831882804</v>
+        <v>30.59833217687932</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1022783188280414</v>
+        <v>0.1583321768793198</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01046085450229049</v>
+        <v>0.0250690782353442</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>30.48</v>
       </c>
       <c r="C9" t="n">
-        <v>30.5519949621441</v>
+        <v>30.39285980145227</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07199496214410317</v>
+        <v>-0.08714019854773269</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005183274574130849</v>
+        <v>0.007593414202938275</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.69</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60082321928214</v>
+        <v>30.42112648669375</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.08917678071786383</v>
+        <v>-0.2688735133062501</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007952498219201971</v>
+        <v>0.07229296615764624</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.75</v>
       </c>
       <c r="C11" t="n">
-        <v>30.76713189625077</v>
+        <v>30.59292177558498</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01713189625076694</v>
+        <v>-0.1570782244150202</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0002935018691470424</v>
+        <v>0.02467356858537544</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.94</v>
       </c>
       <c r="C12" t="n">
-        <v>30.89341029886786</v>
+        <v>30.59609350251453</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.04658970113214522</v>
+        <v>-0.3439064974854666</v>
       </c>
       <c r="E12" t="n">
-        <v>0.002170600251582614</v>
+        <v>0.1182716790127213</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.95</v>
       </c>
       <c r="C13" t="n">
-        <v>31.10379906852334</v>
+        <v>30.68125139573897</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1537990685233375</v>
+        <v>-0.268748604261031</v>
       </c>
       <c r="E13" t="n">
-        <v>0.02365415347864626</v>
+        <v>0.07222581229225224</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>31.02</v>
       </c>
       <c r="C14" t="n">
-        <v>31.27142860609367</v>
+        <v>30.97791601513583</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2514286060936683</v>
+        <v>-0.04208398486417408</v>
       </c>
       <c r="E14" t="n">
-        <v>0.06321634396220505</v>
+        <v>0.001771061782048034</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>31.12</v>
       </c>
       <c r="C15" t="n">
-        <v>31.33366433097254</v>
+        <v>31.18370574024338</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2136643309725379</v>
+        <v>0.06370574024337472</v>
       </c>
       <c r="E15" t="n">
-        <v>0.04565244632994222</v>
+        <v>0.004058421339956333</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>31.28</v>
       </c>
       <c r="C16" t="n">
-        <v>31.1674750055018</v>
+        <v>31.26910170922426</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1125249944982052</v>
+        <v>-0.01089829077574223</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01266187438682111</v>
+        <v>0.0001187727418326281</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>31.38</v>
       </c>
       <c r="C17" t="n">
-        <v>30.93389696060447</v>
+        <v>31.22591499283635</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4461030393955276</v>
+        <v>-0.1540850071636477</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1990079217579277</v>
+        <v>0.02374218943262136</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>31.58</v>
       </c>
       <c r="C18" t="n">
-        <v>31.12874365607843</v>
+        <v>31.50919585364702</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4512563439215675</v>
+        <v>-0.07080414635297672</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2036322879294601</v>
+        <v>0.005013227140773746</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>31.65</v>
       </c>
       <c r="C19" t="n">
-        <v>31.68285551433151</v>
+        <v>31.51390752584824</v>
       </c>
       <c r="D19" t="n">
-        <v>0.03285551433151213</v>
+        <v>-0.1360924741517593</v>
       </c>
       <c r="E19" t="n">
-        <v>0.001079484821988199</v>
+        <v>0.01852116152074727</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.88</v>
       </c>
       <c r="C20" t="n">
-        <v>32.54857965831769</v>
+        <v>32.09524793211833</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6685796583176931</v>
+        <v>0.2152479321183272</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4469987595162032</v>
+        <v>0.04633167228121598</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>32.28</v>
       </c>
       <c r="C21" t="n">
-        <v>32.55971918219023</v>
+        <v>31.94533749013893</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2797191821902274</v>
+        <v>-0.3346625098610758</v>
       </c>
       <c r="E21" t="n">
-        <v>0.07824282088516962</v>
+        <v>0.1119989955065147</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>32.45</v>
       </c>
       <c r="C22" t="n">
-        <v>32.73532906098168</v>
+        <v>32.16284106741204</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2853290609816739</v>
+        <v>-0.287158932587964</v>
       </c>
       <c r="E22" t="n">
-        <v>0.08141267304068377</v>
+        <v>0.08246025256505884</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>32.85</v>
       </c>
       <c r="C23" t="n">
-        <v>32.9375852778052</v>
+        <v>32.84397390644097</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08758527780519643</v>
+        <v>-0.006026093559036383</v>
       </c>
       <c r="E23" t="n">
-        <v>0.007671180888213434</v>
+        <v>3.631380358225978e-05</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>32.9</v>
       </c>
       <c r="C24" t="n">
-        <v>32.99351977061944</v>
+        <v>32.99981149357517</v>
       </c>
       <c r="D24" t="n">
-        <v>0.09351977061943728</v>
+        <v>0.09981149357516728</v>
       </c>
       <c r="E24" t="n">
-        <v>0.008745947496712165</v>
+        <v>0.009962334249705659</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>33.1</v>
       </c>
       <c r="C25" t="n">
-        <v>33.22201537420774</v>
+        <v>32.94013877966522</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1220153742077414</v>
+        <v>-0.1598612203347827</v>
       </c>
       <c r="E25" t="n">
-        <v>0.01488775154305518</v>
+        <v>0.02555560976692593</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>33.4</v>
       </c>
       <c r="C26" t="n">
-        <v>33.51113863081579</v>
+        <v>33.48384629881136</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1111386308157876</v>
+        <v>0.08384629881135908</v>
       </c>
       <c r="E26" t="n">
-        <v>0.01235179525960793</v>
+        <v>0.007030201824363714</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>33.7</v>
       </c>
       <c r="C27" t="n">
-        <v>33.60283648162176</v>
+        <v>33.41505031432929</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.09716351837824533</v>
+        <v>-0.2849496856707177</v>
       </c>
       <c r="E27" t="n">
-        <v>0.009440749303639617</v>
+        <v>0.08119632336384079</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>34.1</v>
       </c>
       <c r="C28" t="n">
-        <v>33.71172498514026</v>
+        <v>33.64382349501036</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3882750148597438</v>
+        <v>-0.4561765049896422</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1507574871643343</v>
+        <v>0.2080970037045651</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>34.4</v>
       </c>
       <c r="C29" t="n">
-        <v>34.29938866808003</v>
+        <v>34.07270144620092</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1006113319199713</v>
+        <v>-0.3272985537990749</v>
       </c>
       <c r="E29" t="n">
-        <v>0.01012264011071063</v>
+        <v>0.1071243433189659</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>34.9</v>
       </c>
       <c r="C30" t="n">
-        <v>34.59425327533567</v>
+        <v>34.68414661604064</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.3057467246643242</v>
+        <v>-0.2158533839593559</v>
       </c>
       <c r="E30" t="n">
-        <v>0.09348105964296206</v>
+        <v>0.04659268336670514</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>35.3</v>
       </c>
       <c r="C31" t="n">
-        <v>35.63727115299272</v>
+        <v>35.33384987923905</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3372711529927201</v>
+        <v>0.03384987923905669</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1137518306410388</v>
+        <v>0.001145814324498721</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>35.7</v>
       </c>
       <c r="C32" t="n">
-        <v>35.89773605532633</v>
+        <v>35.65183726981358</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1977360553263239</v>
+        <v>-0.04816273018642647</v>
       </c>
       <c r="E32" t="n">
-        <v>0.03909954757601502</v>
+        <v>0.002319648579010516</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>36.3</v>
       </c>
       <c r="C33" t="n">
-        <v>36.32664756839336</v>
+        <v>36.20152378428449</v>
       </c>
       <c r="D33" t="n">
-        <v>0.02664756839336491</v>
+        <v>-0.09847621571550746</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0007100929012790603</v>
+        <v>0.00969756506164716</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>36.8</v>
       </c>
       <c r="C34" t="n">
-        <v>36.82917752352359</v>
+        <v>36.82192436800459</v>
       </c>
       <c r="D34" t="n">
-        <v>0.02917752352359315</v>
+        <v>0.02192436800459063</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0008513278789698317</v>
+        <v>0.0004806779124007175</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>37.3</v>
       </c>
       <c r="C35" t="n">
-        <v>36.99573242149806</v>
+        <v>36.99089068355848</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.3042675785019355</v>
+        <v>-0.3091093164415142</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0925787593274315</v>
+        <v>0.09554856951094015</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>37.9</v>
       </c>
       <c r="C36" t="n">
-        <v>37.78072258726555</v>
+        <v>37.71977895034296</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1192774127344478</v>
+        <v>-0.1802210496570353</v>
       </c>
       <c r="E36" t="n">
-        <v>0.01422710118862381</v>
+        <v>0.0324796267394836</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>38.5</v>
       </c>
       <c r="C37" t="n">
-        <v>38.52270208870895</v>
+        <v>38.43745722812026</v>
       </c>
       <c r="D37" t="n">
-        <v>0.02270208870894663</v>
+        <v>-0.06254277187974111</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0005153848317488821</v>
+        <v>0.003911598314401335</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>38.9</v>
       </c>
       <c r="C38" t="n">
-        <v>39.12314879822863</v>
+        <v>38.82118477396173</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2231487982286282</v>
+        <v>-0.07881522603826596</v>
       </c>
       <c r="E38" t="n">
-        <v>0.04979538615088103</v>
+        <v>0.006211839855462957</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>39.4</v>
       </c>
       <c r="C39" t="n">
-        <v>39.44146703013038</v>
+        <v>39.19717767471759</v>
       </c>
       <c r="D39" t="n">
-        <v>0.04146703013037722</v>
+        <v>-0.202822325282412</v>
       </c>
       <c r="E39" t="n">
-        <v>0.001719514587833613</v>
+        <v>0.04113689563296452</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>39.9</v>
       </c>
       <c r="C40" t="n">
-        <v>39.72263802358091</v>
+        <v>39.63644155645955</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1773619764190926</v>
+        <v>-0.2635584435404468</v>
       </c>
       <c r="E40" t="n">
-        <v>0.03145727067928675</v>
+        <v>0.06946305316146287</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>40.1</v>
       </c>
       <c r="C41" t="n">
-        <v>39.7702638787822</v>
+        <v>39.63448174263089</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3297361212177989</v>
+        <v>-0.4655182573691121</v>
       </c>
       <c r="E41" t="n">
-        <v>0.108725909635759</v>
+        <v>0.2167072479439749</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>40.6</v>
       </c>
       <c r="C42" t="n">
-        <v>39.90697336106128</v>
+        <v>39.79900346955557</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.6930266389387256</v>
+        <v>-0.8009965304444364</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4802859222787068</v>
+        <v>0.6415954417840249</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>40.9</v>
       </c>
       <c r="C43" t="n">
-        <v>40.19635090321012</v>
+        <v>40.10096187118257</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.7036490967898743</v>
+        <v>-0.7990381288174291</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4951220514132059</v>
+        <v>0.6384619313040584</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>41.2</v>
       </c>
       <c r="C44" t="n">
-        <v>41.21758245333769</v>
+        <v>41.41359990483372</v>
       </c>
       <c r="D44" t="n">
-        <v>0.01758245333768826</v>
+        <v>0.2135999048337212</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0003091426653719852</v>
+        <v>0.04562491934497474</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>41.5</v>
       </c>
       <c r="C45" t="n">
-        <v>41.28955640879663</v>
+        <v>41.34011962168382</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2104435912033651</v>
+        <v>-0.1598803783161813</v>
       </c>
       <c r="E45" t="n">
-        <v>0.04428650507856904</v>
+        <v>0.02556173537052525</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>41.8</v>
       </c>
       <c r="C46" t="n">
-        <v>41.71509244587822</v>
+        <v>41.60323032321288</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.0849075541217772</v>
+        <v>-0.1967696767871203</v>
       </c>
       <c r="E46" t="n">
-        <v>0.007209292746942523</v>
+        <v>0.0387183057029078</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>42.2</v>
       </c>
       <c r="C47" t="n">
-        <v>42.40166043411897</v>
+        <v>42.54214165114929</v>
       </c>
       <c r="D47" t="n">
-        <v>0.2016604341189705</v>
+        <v>0.3421416511492836</v>
       </c>
       <c r="E47" t="n">
-        <v>0.04066693068905164</v>
+        <v>0.1170609094511581</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>42.7</v>
       </c>
       <c r="C48" t="n">
-        <v>43.53255751544864</v>
+        <v>43.7719924580177</v>
       </c>
       <c r="D48" t="n">
-        <v>0.8325575154486344</v>
+        <v>1.071992458017696</v>
       </c>
       <c r="E48" t="n">
-        <v>0.6931520165300031</v>
+        <v>1.149167830046823</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>43.7</v>
       </c>
       <c r="C49" t="n">
-        <v>43.95549435339204</v>
+        <v>43.99498359662815</v>
       </c>
       <c r="D49" t="n">
-        <v>0.255494353392038</v>
+        <v>0.2949835966281427</v>
       </c>
       <c r="E49" t="n">
-        <v>0.06527736461521558</v>
+        <v>0.08701532227967478</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>44.2</v>
       </c>
       <c r="C50" t="n">
-        <v>44.25777747149995</v>
+        <v>43.83720606269036</v>
       </c>
       <c r="D50" t="n">
-        <v>0.05777747149994639</v>
+        <v>-0.3627939373096467</v>
       </c>
       <c r="E50" t="n">
-        <v>0.003338236212927117</v>
+        <v>0.1316194409486359</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>45.6</v>
       </c>
       <c r="C51" t="n">
-        <v>45.62681281157661</v>
+        <v>44.47711782564872</v>
       </c>
       <c r="D51" t="n">
-        <v>0.02681281157660464</v>
+        <v>-1.122882174351282</v>
       </c>
       <c r="E51" t="n">
-        <v>0.000718926864642504</v>
+        <v>1.260864377475864</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>0.01236847578596567</v>
+        <v>-7.232234026547655</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>3.819149214691712</v>
+        <v>5.96159002397333</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.07638298429383424</v>
+        <v>0.1192318004794666</v>
       </c>
     </row>
   </sheetData>
